--- a/notes/_research/gpu-hardware-scope.xlsx
+++ b/notes/_research/gpu-hardware-scope.xlsx
@@ -16,16 +16,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intel" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Microsoft" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="寒武纪" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="沐曦" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摩尔线程" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="壁仞" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="海光" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Groq" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cerebras" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="昆仑芯" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="寒武纪" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="沐曦" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摩尔线程" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="壁仞" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="海光" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Groq" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cerebras" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'机型清单'!$A$1:$N$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'机型清单'!$A$1:$N$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -549,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2433,9 +2434,219 @@
         </is>
       </c>
     </row>
+    <row r="28" ht="44" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>昆仑芯</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>P800</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>无官方公开参数（仅官方新闻提及型号）</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>无：昆仑芯官网产品信息仅列 R / K 系列，无 P800 规格页</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>XPU</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>NPU</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>量产</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>国产章</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>国产里出货与集群规模最实的一条线：官方新闻确认已通过信通院 DeepSeek 671B 满血版适配、并与 openEuler 完成兼容性互认证</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>官网无规格页，参数全部为「无」；流传的 96 GB / 345 TFLOPS 无官方出处</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="44" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>昆仑芯</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>M100</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>无官方公开参数</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>无：昆仑芯官网无 M 系列页面</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>XPU</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>NPU</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>宣布</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2026 初（计划）</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>国产章附表</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>百度世界大会 2025 公布的第四代，定位大规模推理；用来标注国产路线图的下一跳</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>官网无 M 系列页面，无任何官方参数</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="44" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>昆仑芯</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>M300</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>无官方公开参数</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>无：昆仑芯官网无 M 系列页面</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>XPU</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>NPU</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>宣布</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2027 初（计划）</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>国产章附表</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>同一路线图里面向超大规模多模态训练 / 推理的一代</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>官网无 M 系列页面，无任何官方参数</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N27"/>
-  <conditionalFormatting sqref="M2:M27">
+  <autoFilter ref="A1:N30"/>
+  <conditionalFormatting sqref="M2:M30">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"低"</formula>
     </cfRule>
@@ -2444,10 +2655,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" error="只能是 P0 / P1 / P2" type="list">
+    <dataValidation sqref="B2:B30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" error="只能是 P0 / P1 / P2" type="list">
       <formula1>"P0,P1,P2"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M2:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2484,21 +2695,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>寒武纪 · 官方参数</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="48" customHeight="1">
+          <t>昆仑芯 · 官方参数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>只收厂商白皮书、datasheet、官网规格页与官方博客 / 文档里写明的数；原文没写的一律填「无」，不换算、不由整机反推单卡；稀疏 / 稠密照原文标注。①②③ 对应表底的来源。核对日期 2026-10-26。</t>
@@ -2513,11 +2726,21 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>思元 690</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
+          <t>P800</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>M100</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>M300</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="90" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>简介（据官方文档）</t>
@@ -2525,7 +2748,17 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>无：寒武纪官网产品页仅列至思元 370（MLU370），未发布思元 690 的规格或白皮书</t>
+          <t>无官方规格：昆仑芯官网「产品信息」只列 R 系列（昆仑芯 2 代、R100、R200、RG800、R480-X8）与 K 系列（昆仑芯 1 代、K100、K200），未发布 P800 的规格页或白皮书 ③；官方新闻确认该型号存在且已规模交付 ①②</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>无：昆仑芯官网未发布 M100 的规格页或白皮书，站内新闻也未出现该型号；型号与定位（面向大规模推理、计划 2026 年初上市）出自 2025-11-13 百度世界大会的公开发布</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>无：昆仑芯官网未发布 M300 的规格页或白皮书，站内新闻也未出现该型号；型号与定位（面向超大规模多模态模型训练与推理、计划 2027 年初上市）出自 2025-11-13 百度世界大会的公开发布</t>
         </is>
       </c>
     </row>
@@ -2540,6 +2773,16 @@
           <t>无</t>
         </is>
       </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
@@ -2552,6 +2795,16 @@
           <t>无</t>
         </is>
       </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -2564,6 +2817,16 @@
           <t>无</t>
         </is>
       </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
@@ -2576,6 +2839,16 @@
           <t>无</t>
         </is>
       </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
@@ -2588,6 +2861,16 @@
           <t>无</t>
         </is>
       </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
@@ -2600,6 +2883,16 @@
           <t>无</t>
         </is>
       </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
@@ -2612,6 +2905,16 @@
           <t>无</t>
         </is>
       </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
@@ -2624,6 +2927,16 @@
           <t>无</t>
         </is>
       </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
@@ -2636,6 +2949,16 @@
           <t>无</t>
         </is>
       </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
@@ -2648,6 +2971,16 @@
           <t>无</t>
         </is>
       </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
@@ -2660,6 +2993,16 @@
           <t>无</t>
         </is>
       </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -2672,6 +3015,16 @@
           <t>无</t>
         </is>
       </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
@@ -2684,6 +3037,16 @@
           <t>无</t>
         </is>
       </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
@@ -2696,6 +3059,16 @@
           <t>无</t>
         </is>
       </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
@@ -2708,6 +3081,16 @@
           <t>无</t>
         </is>
       </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
@@ -2720,6 +3103,16 @@
           <t>无</t>
         </is>
       </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
@@ -2732,6 +3125,16 @@
           <t>无</t>
         </is>
       </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
@@ -2744,32 +3147,62 @@
           <t>无</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="104" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
           <t>其他官方指标</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>官方新闻口径：P800 单机 8 卡一体机通过中国信通院 DeepSeek-V3/R1 671B 满血版适配支持性测试，精度与 DeepSeek 技术报告对齐、支持长上下文推理，为首个通过该测试的产品 ①；P800 系列与 openEuler 完成兼容性互认证，七项子测试全部通过 ②</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="90" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
           <t>口径说明</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="34" customHeight="1">
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>官方新闻只写适配与认证结果，未给出显存、算力、带宽、功耗等任何参数，故本列参数全部为「无」；流传的 96 GB HBM、345 TFLOPS FP16、2.4 TB/s 等数字均出自媒体报道，未见官方文档，不予采信</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>本列无任何官方参数。大会路线图只给定位与上市时间，且未见官方文档原文，故不填入参数行</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>本列无任何官方参数。大会路线图只给定位与上市时间，且未见官方文档原文，故不填入参数行</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="76" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
           <t>来源 ①</t>
@@ -2777,18 +3210,80 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>已核查：寒武纪官网产品中心（无思元 690）
-https://www.cambricon.com/</t>
+          <t>官方新闻：昆仑芯 · 首个！昆仑芯 P800 单机 8 卡一体机通过中国信通院 DeepSeek 适配测试（2025-04-17）
+https://www.kunlunxin.com/news/4471.html</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>已核查：昆仑芯官网产品信息（无 M 系列页面）
+https://www.kunlunxin.com/</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>已核查：昆仑芯官网产品信息（无 M 系列页面）
+https://www.kunlunxin.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="62" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>来源 ②</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>官方新闻：昆仑芯 · 与 openEuler 完成兼容性互认证（2026-10-23）
+https://www.kunlunxin.com/news/5195.html</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>来源 ③</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>已核查：昆仑芯官网产品信息（仅列 R / K 系列，无 P800 规格页）
+https://www.kunlunxin.com/</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2810,7 +3305,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>沐曦 · 官方参数</t>
+          <t>寒武纪 · 官方参数</t>
         </is>
       </c>
     </row>
@@ -2829,19 +3324,19 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>曦云 C600</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="48" customHeight="1">
+          <t>思元 690</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>简介（据官方文档）</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>沐曦基于自主知识产权 GPGPU 架构与国产先进工艺研发的新一代通用 GPU，面向智算中心、通用计算与数据分析；配 MXMACA 软件栈（兼容主流 GPU 生态）</t>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>无：寒武纪官网产品页仅列至思元 370（MLU370），未发布思元 690 的规格或白皮书</t>
         </is>
       </c>
     </row>
@@ -2851,9 +3346,9 @@
           <t>架构</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>自主知识产权 GPGPU 架构（未写代号）</t>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
@@ -2863,9 +3358,9 @@
           <t>制程 / 晶体管 / 封装</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>国产先进工艺（未写节点）</t>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
@@ -2875,9 +3370,9 @@
           <t>形态 / 散热</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>OAM 2.0 扣卡式模组；风冷 / 液冷</t>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
@@ -2889,7 +3384,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>无（官网仅称「超大容量高带宽显存」，支持全链路 ECC）</t>
+          <t>无</t>
         </is>
       </c>
     </row>
@@ -3019,9 +3514,9 @@
           <t>Scale-up 互连</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>MetaXLink 互连；MetaXLink-E 接口最高 128 卡超节点</t>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
@@ -3043,9 +3538,9 @@
           <t>功耗</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>最大功耗 1000W</t>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
@@ -3093,8 +3588,8 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>官网产品页：沐曦 · 曦云C600
-https://www.metax-tech.com/prod.html?cid=107&amp;id=68</t>
+          <t>已核查：寒武纪官网产品中心（无思元 690）
+https://www.cambricon.com/</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3126,7 +3621,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>摩尔线程 · 官方参数</t>
+          <t>沐曦 · 官方参数</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3640,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>MTT S5000</t>
+          <t>曦云 C600</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3652,7 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>搭载新一代 PH100 芯片的全功能 GPU 智算卡，面向大模型训练、推理与高性能计算；第四代 MUSA「平湖」架构，支持 FP8 到 FP64 全精度 ①</t>
+          <t>沐曦基于自主知识产权 GPGPU 架构与国产先进工艺研发的新一代通用 GPU，面向智算中心、通用计算与数据分析；配 MXMACA 软件栈（兼容主流 GPU 生态）</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3664,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>平湖（第四代 MUSA 架构），含 TCE / TME / ACE 三大引擎 ②</t>
+          <t>自主知识产权 GPGPU 架构（未写代号）</t>
         </is>
       </c>
     </row>
@@ -3179,9 +3674,9 @@
           <t>制程 / 晶体管 / 封装</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>无</t>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>国产先进工艺（未写节点）</t>
         </is>
       </c>
     </row>
@@ -3193,7 +3688,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>OAM 计算模组，液冷版 / 风冷版 ①</t>
+          <t>OAM 2.0 扣卡式模组；风冷 / 液冷</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3700,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>无（官网仅称「超大容量高带宽显存」，支持全链路 ECC）</t>
         </is>
       </c>
     </row>
@@ -3257,7 +3752,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="34" customHeight="1">
+    <row r="14" ht="20" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>FP8 / MXFP8</t>
@@ -3265,7 +3760,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>无（官方只写原生支持 FP8 的 E4M3 / E5M2 格式，未给算力数值）①②</t>
+          <t>无</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3824,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="34" customHeight="1">
+    <row r="20" ht="20" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Scale-up 互连</t>
@@ -3337,7 +3832,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>第二代 MTLink，官方称带宽为上一代 7 倍、支持节点内 8 卡全连接（未给绝对值）②</t>
+          <t>MetaXLink 互连；MetaXLink-E 接口最高 128 卡超节点</t>
         </is>
       </c>
     </row>
@@ -3359,9 +3854,9 @@
           <t>功耗</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>无</t>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>最大功耗 1000W</t>
         </is>
       </c>
     </row>
@@ -3389,15 +3884,15 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="34" customHeight="1">
+    <row r="25" ht="20" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
           <t>口径说明</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>产品页脚注里的 989 TFLOPS / 3.35TB/s 等是对标的「国际旗舰产品」参数，不是 S5000 自身规格 ①</t>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
@@ -3409,21 +3904,8 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>官网产品页：摩尔线程 · MTT S5000
-https://www.mthreads.com/product/S5000</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>来源 ②</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>官网架构页：摩尔线程 ·「平湖」架构
-https://www.mthreads.com/architecture/pinghu</t>
+          <t>官网产品页：沐曦 · 曦云C600
+https://www.metax-tech.com/prod.html?cid=107&amp;id=68</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3916,6 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3446,7 +3927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3456,7 +3937,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>壁仞 · 官方参数</t>
+          <t>摩尔线程 · 官方参数</t>
         </is>
       </c>
     </row>
@@ -3475,19 +3956,19 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>BR104</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
+          <t>MTT S5000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>简介（据官方文档）</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>无：壁仞官网现仅列壁砺 106 / 166 系列；原 BR100 系列页面（birentech.com/BR10X.html）已 404，未见 BR104 官方规格</t>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>搭载新一代 PH100 芯片的全功能 GPU 智算卡，面向大模型训练、推理与高性能计算；第四代 MUSA「平湖」架构，支持 FP8 到 FP64 全精度 ①</t>
         </is>
       </c>
     </row>
@@ -3497,9 +3978,9 @@
           <t>架构</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>无</t>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>平湖（第四代 MUSA 架构），含 TCE / TME / ACE 三大引擎 ②</t>
         </is>
       </c>
     </row>
@@ -3521,9 +4002,9 @@
           <t>形态 / 散热</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>无</t>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>OAM 计算模组，液冷版 / 风冷版 ①</t>
         </is>
       </c>
     </row>
@@ -3587,7 +4068,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
+    <row r="14" ht="34" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>FP8 / MXFP8</t>
@@ -3595,7 +4076,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>无（官方只写原生支持 FP8 的 E4M3 / E5M2 格式，未给算力数值）①②</t>
         </is>
       </c>
     </row>
@@ -3659,15 +4140,15 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
+    <row r="20" ht="34" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Scale-up 互连</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>无</t>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>第二代 MTLink，官方称带宽为上一代 7 倍、支持节点内 8 卡全连接（未给绝对值）②</t>
         </is>
       </c>
     </row>
@@ -3719,15 +4200,15 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1">
+    <row r="25" ht="34" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
           <t>口径说明</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>无</t>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>产品页脚注里的 989 TFLOPS / 3.35TB/s 等是对标的「国际旗舰产品」参数，不是 S5000 自身规格 ①</t>
         </is>
       </c>
     </row>
@@ -3739,8 +4220,21 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>已核查：壁仞官网产品服务（无 BR104）
-https://www.birentech.com/</t>
+          <t>官网产品页：摩尔线程 · MTT S5000
+https://www.mthreads.com/product/S5000</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>来源 ②</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>官网架构页：摩尔线程 ·「平湖」架构
+https://www.mthreads.com/architecture/pinghu</t>
         </is>
       </c>
     </row>
@@ -3751,6 +4245,7 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3772,7 +4267,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>海光 · 官方参数</t>
+          <t>壁仞 · 官方参数</t>
         </is>
       </c>
     </row>
@@ -3791,7 +4286,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>DCU3G</t>
+          <t>BR104</t>
         </is>
       </c>
     </row>
@@ -3803,7 +4298,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>无：未找到海光官方公开的 DCU 规格或白皮书</t>
+          <t>无：壁仞官网现仅列壁砺 106 / 166 系列；原 BR100 系列页面（birentech.com/BR10X.html）已 404，未见 BR104 官方规格</t>
         </is>
       </c>
     </row>
@@ -4055,8 +4550,8 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>已核查：海光官网（未见 DCU 规格）
-https://www.hygon.cn/</t>
+          <t>已核查：壁仞官网产品服务（无 BR104）
+https://www.birentech.com/</t>
         </is>
       </c>
     </row>
@@ -4078,6 +4573,322 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>海光 · 官方参数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>只收厂商白皮书、datasheet、官网规格页与官方博客 / 文档里写明的数；原文没写的一律填「无」，不换算、不由整机反推单卡；稀疏 / 稠密照原文标注。①②③ 对应表底的来源。核对日期 2026-10-26。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>字段</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>DCU3G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>简介（据官方文档）</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>无：未找到海光官方公开的 DCU 规格或白皮书</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>架构</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>制程 / 晶体管 / 封装</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>形态 / 散热</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>显存容量</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>显存类型</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>显存带宽</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>片上 SRAM / 缓存</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>FP4 / MXFP4</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>FP8 / MXFP8</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>BF16 / FP16</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>TF32</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>FP32</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>FP64</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>INT8</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Scale-up 互连</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Scale-out / 主机接口</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>功耗</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>发布 / 上市（官方表述）</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>其他官方指标</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>口径说明</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>来源 ①</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>已核查：海光官网（未见 DCU 规格）
+https://www.hygon.cn/</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4402,7 +5213,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
